--- a/VerveStacks_CHE_grids/SysSettings.xlsx
+++ b/VerveStacks_CHE_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F101EF-4ECC-4CCC-8F5B-CE852A3FC1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3D34F-2C34-4BAD-8F27-4A824FBF2E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4568,7 +4568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F47C7549-C8A1-479B-B0E7-060E0B595B95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B8525A-9846-4AB9-891B-E1082948C7B6}">
   <dimension ref="B3:H197"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SysSettings.xlsx
+++ b/VerveStacks_CHE_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3D34F-2C34-4BAD-8F27-4A824FBF2E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4754E410-ABFF-4648-A6FF-888DDE064C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4568,7 +4568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B8525A-9846-4AB9-891B-E1082948C7B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B09D17-6A0E-425E-A3B0-9887EE277DDE}">
   <dimension ref="B3:H197"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SysSettings.xlsx
+++ b/VerveStacks_CHE_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4754E410-ABFF-4648-A6FF-888DDE064C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E689CA9F-EBE0-4EFC-BDF3-8AB9CA6DAEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4568,7 +4568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B09D17-6A0E-425E-A3B0-9887EE277DDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923EBC85-6C3C-4F02-883B-14DF97D98072}">
   <dimension ref="B3:H197"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SysSettings.xlsx
+++ b/VerveStacks_CHE_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E689CA9F-EBE0-4EFC-BDF3-8AB9CA6DAEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1838C7-CB75-49A9-945C-AE6F0D8FC0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4568,7 +4568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923EBC85-6C3C-4F02-883B-14DF97D98072}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38C3CFB-CB36-47C8-9EAB-63A609A2FF0A}">
   <dimension ref="B3:H197"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SysSettings.xlsx
+++ b/VerveStacks_CHE_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1838C7-CB75-49A9-945C-AE6F0D8FC0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47ADC3E-0D87-4562-98AA-AB408B28D6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4568,7 +4568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38C3CFB-CB36-47C8-9EAB-63A609A2FF0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B2F002-858E-4880-BED4-35066ACAD99C}">
   <dimension ref="B3:H197"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
